--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationpregnancyoutcome.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="447">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,10 +653,13 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-pregnanciessummary</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -901,6 +904,9 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -987,9 +993,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1368,12 +1371,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1744,7 +1741,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.07421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3641,9 +3638,11 @@
       <c r="X16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3676,30 +3675,30 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3722,19 +3721,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3783,7 +3782,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3798,19 +3797,19 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3818,10 +3817,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3844,16 +3843,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3903,7 +3902,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3924,13 +3923,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3938,14 +3937,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3964,19 +3963,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4025,7 +4024,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4040,19 +4039,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4060,14 +4059,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4086,19 +4085,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4147,7 +4146,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4162,19 +4161,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4182,10 +4181,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4208,16 +4207,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4267,7 +4266,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4288,13 +4287,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4302,10 +4301,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4328,17 +4327,17 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4387,7 +4386,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4402,19 +4401,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4422,10 +4421,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4448,19 +4447,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4509,7 +4508,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4518,7 +4517,7 @@
         <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
@@ -4527,27 +4526,27 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4573,16 +4572,16 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4607,13 +4606,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4631,7 +4630,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4640,7 +4639,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4655,7 +4654,7 @@
         <v>135</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4666,14 +4665,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4695,16 +4694,16 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4729,13 +4728,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4753,7 +4752,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4771,27 +4770,27 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4814,19 +4813,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4875,7 +4874,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4896,10 +4895,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4910,10 +4909,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4939,13 +4938,13 @@
         <v>190</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4971,13 +4970,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4995,7 +4994,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5013,27 +5012,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5059,16 +5058,16 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5093,13 +5092,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5117,7 +5116,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5138,10 +5137,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5152,10 +5151,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5178,16 +5177,16 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5237,7 +5236,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5255,27 +5254,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5298,16 +5297,16 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5357,7 +5356,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5375,27 +5374,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5418,19 +5417,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5479,7 +5478,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5491,7 +5490,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5500,10 +5499,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5514,10 +5513,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5540,13 +5539,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5597,7 +5596,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5621,7 +5620,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5632,10 +5631,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5664,7 +5663,7 @@
         <v>139</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>141</v>
@@ -5717,7 +5716,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5741,7 +5740,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5752,14 +5751,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5781,10 +5780,10 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
@@ -5839,7 +5838,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5874,10 +5873,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5900,13 +5899,13 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5957,7 +5956,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5966,7 +5965,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
@@ -5978,10 +5977,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5992,10 +5991,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6018,13 +6017,13 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6075,7 +6074,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6084,7 +6083,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6096,10 +6095,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6110,10 +6109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6139,16 +6138,16 @@
         <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6176,10 +6175,10 @@
         <v>116</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6197,7 +6196,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6215,13 +6214,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6232,10 +6231,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6261,16 +6260,16 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6295,13 +6294,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6319,7 +6318,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6337,13 +6336,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6354,10 +6353,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6380,17 +6379,17 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6439,7 +6438,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6463,7 +6462,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6474,10 +6473,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6500,13 +6499,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6557,7 +6556,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6578,10 +6577,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6592,10 +6591,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6618,16 +6617,16 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6677,7 +6676,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6698,10 +6697,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6712,10 +6711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6738,16 +6737,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6797,7 +6796,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6818,10 +6817,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6832,10 +6831,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6858,19 +6857,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6919,7 +6918,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6940,10 +6939,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6954,10 +6953,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6980,13 +6979,13 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7037,7 +7036,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7061,7 +7060,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7072,10 +7071,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7104,7 +7103,7 @@
         <v>139</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>141</v>
@@ -7157,7 +7156,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7181,7 +7180,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7192,14 +7191,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7221,10 +7220,10 @@
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7279,7 +7278,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7314,10 +7313,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7343,13 +7342,13 @@
         <v>190</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>204</v>
@@ -7377,13 +7376,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>433</v>
+        <v>206</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>434</v>
+        <v>207</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7401,7 +7400,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>92</v>
@@ -7419,16 +7418,16 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7436,10 +7435,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7462,19 +7461,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7523,7 +7522,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7541,27 +7540,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7587,16 +7586,16 @@
         <v>190</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7621,13 +7620,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7645,7 +7644,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7654,7 +7653,7 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7669,7 +7668,7 @@
         <v>135</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7680,14 +7679,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7709,16 +7708,16 @@
         <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7743,13 +7742,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7767,7 +7766,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7785,27 +7784,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7831,16 +7830,16 @@
         <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7889,7 +7888,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7910,10 +7909,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
